--- a/用卷/xlsx/1952,1953.xlsx
+++ b/用卷/xlsx/1952,1953.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7A7DD7-C78A-41DC-AAFB-5C6FED246557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C0A592-AC7C-4E38-B41C-B19C24363494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
   <si>
     <t>年份</t>
   </si>
@@ -58,10 +58,6 @@
   </si>
   <si>
     <t>政治</t>
-  </si>
-  <si>
-    <t>说明</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>全国卷</t>
@@ -235,7 +231,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -253,12 +249,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -266,15 +256,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -566,116 +547,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="13"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="C3" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C4" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="11"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="11"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="8"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="8"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="8"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="18"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B10" s="12"/>
+      <c r="C10" s="13"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>2</v>
       </c>
@@ -686,7 +656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
@@ -694,10 +664,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>6</v>
       </c>
@@ -705,21 +675,21 @@
         <v>1</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
-        <v>21</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="B14" s="4">
         <v>1</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
@@ -727,10 +697,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>8</v>
       </c>
@@ -738,32 +708,32 @@
         <v>1</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="B17" s="4">
         <v>1</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
-        <v>22</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="B18" s="4">
         <v>1</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>9</v>
       </c>
@@ -771,41 +741,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D33" s="6"/>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D34" s="6"/>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D35" s="6"/>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D36" s="6"/>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D37" s="6"/>
-    </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D38" s="12"/>
-    </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D39" s="12"/>
-    </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D40" s="6"/>
-    </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D41" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
